--- a/data/汇总持仓.xlsx
+++ b/data/汇总持仓.xlsx
@@ -1469,7 +1469,7 @@
         <v>867.62</v>
       </c>
       <c r="K13" s="2">
-        <v>0</v>
+        <v>0.0708</v>
       </c>
       <c r="L13" t="str">
         <v/>
